--- a/cypress/downloads/Agent Performance Report_20251207.xlsx
+++ b/cypress/downloads/Agent Performance Report_20251207.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>Agent Name</t>
   </si>
@@ -56,7 +56,7 @@
     <t>mdesouky@victorylink.com</t>
   </si>
   <si>
-    <t>2527:00</t>
+    <t>2533:04</t>
   </si>
   <si>
     <t>1507:52</t>
@@ -110,51 +110,12 @@
     <t>NellyMohamed@gmail.com</t>
   </si>
   <si>
-    <t>New Mohamed</t>
-  </si>
-  <si>
-    <t>NewMohamed@gmail.com</t>
-  </si>
-  <si>
-    <t>hythamvl</t>
-  </si>
-  <si>
-    <t>hkhalifa@victorylink.com</t>
-  </si>
-  <si>
-    <t>2747:55</t>
-  </si>
-  <si>
-    <t>Mahmoud</t>
-  </si>
-  <si>
-    <t>mahmoud@gmail.com</t>
-  </si>
-  <si>
     <t>kamal</t>
   </si>
   <si>
     <t>kamal@gmail.com</t>
   </si>
   <si>
-    <t>ragab</t>
-  </si>
-  <si>
-    <t>ragab@gamil.com</t>
-  </si>
-  <si>
-    <t>yahia</t>
-  </si>
-  <si>
-    <t>yahia@gmail.com</t>
-  </si>
-  <si>
-    <t>Mossa Mohamed</t>
-  </si>
-  <si>
-    <t>MossaMohamed@gmail.com</t>
-  </si>
-  <si>
     <t>May Mohamed</t>
   </si>
   <si>
@@ -305,24 +266,12 @@
     <t>sdfsdf@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Desouky  502</t>
-  </si>
-  <si>
-    <t>Desouky29999@ntchnco.com630</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desouky  140</t>
   </si>
   <si>
     <t>Desouky@ntchnco.com489</t>
   </si>
   <si>
-    <t xml:space="preserve">Desouky  371</t>
-  </si>
-  <si>
-    <t>Desouky@ntchnco.com400</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desouky  319</t>
   </si>
   <si>
@@ -341,12 +290,6 @@
     <t>Desouky@ntchnco.com332</t>
   </si>
   <si>
-    <t xml:space="preserve">Desouky  644</t>
-  </si>
-  <si>
-    <t>Desouky@ntchnco.com812</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desouky  116</t>
   </si>
   <si>
@@ -383,10 +326,22 @@
     <t>Desouky29999@ntchnco.com596</t>
   </si>
   <si>
-    <t xml:space="preserve">Desouky  935</t>
-  </si>
-  <si>
-    <t>Desouky29999@ntchnco.com370</t>
+    <t xml:space="preserve">Desouky  510</t>
+  </si>
+  <si>
+    <t>Desouky29999@ntchnco.com522</t>
+  </si>
+  <si>
+    <t>rarrrr</t>
+  </si>
+  <si>
+    <t>ranamagdyy22@gmail.com555</t>
+  </si>
+  <si>
+    <t>raararra</t>
+  </si>
+  <si>
+    <t>ranamagdyy20002@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -443,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,38 +579,38 @@
         <v>35</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -669,10 +624,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -686,10 +641,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
@@ -703,10 +658,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -720,44 +675,44 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -771,10 +726,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -788,10 +743,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -805,10 +760,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -822,10 +777,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -839,10 +794,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -856,10 +811,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -873,10 +828,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -890,10 +845,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -907,10 +862,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -924,10 +879,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -941,10 +896,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -958,10 +913,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -975,10 +930,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -992,10 +947,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1009,10 +964,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1026,10 +981,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1043,10 +998,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -1060,10 +1015,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1077,10 +1032,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1094,10 +1049,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1111,10 +1066,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1128,10 +1083,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1145,10 +1100,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1162,10 +1117,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1179,10 +1134,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1196,10 +1151,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1213,11 +1168,11 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
@@ -1225,125 +1180,6 @@
         <v>7</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="2">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" s="2">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" s="2">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="2">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="2">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="2">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="s">
         <v>7</v>
       </c>
     </row>
